--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="370">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation Durchgeführte Abgabe</t>
+    <t>ELGA e-Med Durchgeführte Abgabe</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>**Beschreibung:** ELGA e-Med Durchgeführte Abgabe ("List"-MedicationDispense) - noch anzupassen</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1403,67 +1406,67 @@
         <v>22</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1520,135 +1523,135 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1656,10 +1659,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>21</v>
@@ -1671,13 +1674,13 @@
         <v>21</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1728,25 +1731,25 @@
         <v>21</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>21</v>
@@ -1760,10 +1763,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1771,10 +1774,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>21</v>
@@ -1783,19 +1786,19 @@
         <v>21</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1845,13 +1848,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -1877,10 +1880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1888,10 +1891,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>21</v>
@@ -1900,16 +1903,16 @@
         <v>21</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1960,19 +1963,19 @@
         <v>21</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -1992,10 +1995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2003,31 +2006,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2077,19 +2080,19 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2109,10 +2112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2120,10 +2123,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2135,16 +2138,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2170,13 +2173,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -2194,19 +2197,19 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2226,21 +2229,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -2252,16 +2255,16 @@
         <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2311,25 +2314,25 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
@@ -2343,21 +2346,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2369,16 +2372,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2428,13 +2431,13 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
@@ -2446,7 +2449,7 @@
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2460,21 +2463,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2486,16 +2489,16 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2545,25 +2548,25 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2577,45 +2580,45 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -2664,25 +2667,25 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>21</v>
@@ -2696,10 +2699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2707,10 +2710,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2722,16 +2725,16 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2781,31 +2784,31 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>21</v>
@@ -2813,10 +2816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2824,10 +2827,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2839,13 +2842,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2896,25 +2899,25 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -2928,10 +2931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2939,31 +2942,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2989,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3013,31 +3016,31 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>21</v>
@@ -3045,10 +3048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3056,10 +3059,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3071,13 +3074,13 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3104,13 +3107,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3128,25 +3131,25 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3160,10 +3163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3171,10 +3174,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3186,16 +3189,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3221,13 +3224,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3245,25 +3248,25 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3277,10 +3280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3288,10 +3291,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3300,19 +3303,19 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3338,13 +3341,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3362,42 +3365,42 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3405,10 +3408,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3417,19 +3420,19 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3479,42 +3482,42 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3522,10 +3525,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3537,13 +3540,13 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3594,25 +3597,25 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3626,10 +3629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3637,10 +3640,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3652,13 +3655,13 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3709,28 +3712,28 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -3741,10 +3744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3752,10 +3755,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3767,13 +3770,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3824,25 +3827,25 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3856,10 +3859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3867,10 +3870,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3882,13 +3885,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3939,13 +3942,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -3957,7 +3960,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -3971,21 +3974,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -3997,16 +4000,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4056,25 +4059,25 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4088,45 +4091,45 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4175,25 +4178,25 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4207,10 +4210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4218,10 +4221,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4233,17 +4236,17 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4268,13 +4271,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4292,25 +4295,25 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4324,10 +4327,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4335,10 +4338,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4350,13 +4353,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4407,25 +4410,25 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4439,10 +4442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4450,10 +4453,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4465,13 +4468,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4522,25 +4525,25 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4554,10 +4557,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4565,10 +4568,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4580,16 +4583,16 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4639,42 +4642,42 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4682,10 +4685,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4697,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4730,13 +4733,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4754,42 +4757,42 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4797,10 +4800,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4812,13 +4815,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4869,42 +4872,42 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4912,10 +4915,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4927,13 +4930,13 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4984,25 +4987,25 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5011,15 +5014,15 @@
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5027,10 +5030,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5039,16 +5042,16 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5099,42 +5102,42 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5142,10 +5145,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5157,13 +5160,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5214,42 +5217,42 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5257,10 +5260,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5272,13 +5275,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5329,42 +5332,42 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5372,10 +5375,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5387,13 +5390,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5444,31 +5447,31 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -5476,10 +5479,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5487,10 +5490,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5502,13 +5505,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5559,25 +5562,25 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5586,15 +5589,15 @@
         <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5602,10 +5605,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5617,16 +5620,16 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5676,25 +5679,25 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5708,10 +5711,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5719,10 +5722,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5734,13 +5737,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5791,31 +5794,31 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -5823,10 +5826,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5834,10 +5837,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -5849,13 +5852,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5906,13 +5909,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -5924,7 +5927,7 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5938,21 +5941,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -5964,16 +5967,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6023,25 +6026,25 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6055,45 +6058,45 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6142,25 +6145,25 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6174,10 +6177,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6185,10 +6188,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6200,13 +6203,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6257,25 +6260,25 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6289,10 +6292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6300,10 +6303,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6315,13 +6318,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6348,13 +6351,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6372,42 +6375,42 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6415,10 +6418,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -6430,13 +6433,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6463,13 +6466,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6487,31 +6490,31 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6519,10 +6522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6530,10 +6533,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6545,13 +6548,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6602,31 +6605,31 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
@@ -6634,21 +6637,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6660,16 +6663,16 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6719,25 +6722,25 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6751,10 +6754,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6762,10 +6765,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6777,16 +6780,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6836,25 +6839,25 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:27:43+00:00</t>
+    <t>2026-01-30T14:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="408">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** ELGA e-Med Durchgeführte Abgabe ("List"-MedicationDispense) - noch anzupassen</t>
+    <t>**Beschreibung:** Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
+Sofern eine zugehörige geplante Abgabe vorliegt, können Abweichungen hinsichtlich der Dosierung oder einer möglichen
+Substitution des Medikaments in der durchgeführten Abgabe dokumentiert werden.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -262,7 +267,7 @@
 </t>
   </si>
   <si>
-    <t>Dispensing a medication to a named patient</t>
+    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zum Medikationsplan. Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>
@@ -472,7 +477,7 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
+    <t>Externer Identifier.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -500,7 +505,7 @@
 </t>
   </si>
   <si>
-    <t>Event that dispense is part of</t>
+    <t>Auslösendes Ereignis. Verwendung in der durchgeführten Abgabe prüfen.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -515,7 +520,8 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>preparation | in-progress | cancelled | on-hold | completed | entered-in-error | stopped | declined | unknown</t>
+    <t>Status des durchgeführten Abgabe: preparation | in-progress | cancelled | on-hold | completed | entered-in-error | stopped | declined | unknown; http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
+-&gt; VS einschränken</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -546,41 +552,66 @@
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(DetectedIssue|4.0.1)</t>
-  </si>
-  <si>
-    <t>Why a dispense was not performed</t>
-  </si>
-  <si>
-    <t>Indicates the reason why a dispense was not performed.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A code describing why a dispense was not performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.statusReason</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON]/target[classCode=OBS,moodCode=EVN, code="not done reason"].value</t>
-  </si>
-  <si>
-    <t>MedicationDispense.category</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Type of medication dispense</t>
+    <t>Warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
+  </si>
+  <si>
+    <t>Indicates the reason why a dispense was not performed.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A code describing why a dispense was not performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON]/target[classCode=OBS,moodCode=EVN, code="not done reason"].value</t>
+  </si>
+  <si>
+    <t>MedicationDispense.statusReason[x]:statusReasonCodeableConcept</t>
+  </si>
+  <si>
+    <t>statusReasonCodeableConcept</t>
+  </si>
+  <si>
+    <t>Bsp: https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
+  </si>
+  <si>
+    <t>MedicationDispense.statusReason[x]:statusReasonReference</t>
+  </si>
+  <si>
+    <t>statusReasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DetectedIssue)
+</t>
+  </si>
+  <si>
+    <t>Verwendung in der durchgeführten Abgabe prüfen.</t>
+  </si>
+  <si>
+    <t>MedicationDispense.category</t>
+  </si>
+  <si>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant), https://hl7.org/fhir/R4/valueset-medicationdispense-category.html. Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -602,10 +633,10 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|4.0.1)</t>
-  </si>
-  <si>
-    <t>What medication was supplied</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
+  </si>
+  <si>
+    <t>Abgegebenes Medikament. Code oder Referenz</t>
   </si>
   <si>
     <t>Identifies the medication being administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -620,6 +651,9 @@
     <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -635,14 +669,125 @@
     <t>RXD-2-Dispense/Give Code</t>
   </si>
   <si>
+    <t>MedicationDispense.medication[x]:medicationCodeableConcept</t>
+  </si>
+  <si>
+    <t>medicationCodeableConcept</t>
+  </si>
+  <si>
+    <t>Angabe mittels Pharmazentralnummer (PZN) aus der ASP-Liste.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x]:medicationCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x].id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x]:medicationCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x].extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x]:medicationCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>MedicationDispense.medication[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
-    <t>Who the dispense is for</t>
+    <t>Österreichischer Patient für den die durchgeführte Abgabe ausgestellt wird.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -670,7 +815,7 @@
 </t>
   </si>
   <si>
-    <t>Encounter / Episode associated with event</t>
+    <t>Referenz auf Encounter oder EpisodeOfCare. Verwendung in der durchgeführten Abgabe prüfen.</t>
   </si>
   <si>
     <t>The encounter or episode of care that establishes the context for this event.</t>
@@ -689,7 +834,8 @@
 </t>
   </si>
   <si>
-    <t>Information that supports the dispensing of the medication</t>
+    <t>Referenz auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. 
+Verwendung in der durchgeführten Abgabe prüfen.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -708,7 +854,7 @@
 </t>
   </si>
   <si>
-    <t>Who performed event</t>
+    <t>Durchführende Person</t>
   </si>
   <si>
     <t>Indicates who or what performed the event.</t>
@@ -723,29 +869,7 @@
     <t>MedicationDispense.performer.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationDispense.performer.modifierExtension</t>
@@ -768,7 +892,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Who performed the dispense and what they did</t>
+    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Verwendung in der durchgeführten Abgabe prüfen.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -789,11 +913,11 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
-    <t>Individual who was performing</t>
+    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization; entfernen: Patient, Device, RelatedPerson</t>
   </si>
   <si>
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
@@ -812,7 +936,7 @@
 </t>
   </si>
   <si>
-    <t>Where the dispense occurred</t>
+    <t>Ort der Abgabe (Referenz auf Location Ressource). Verwendung prüfen.</t>
   </si>
   <si>
     <t>The principal physical location where the dispense was performed.</t>
@@ -828,7 +952,7 @@
 </t>
   </si>
   <si>
-    <t>Medication order that authorizes the dispense</t>
+    <t>Referenz auf zugehörige geplante Abgabe.</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -852,7 +976,8 @@
     <t>MedicationDispense.type</t>
   </si>
   <si>
-    <t>Trial fill, partial fill, emergency fill, etc.</t>
+    <t>Mögliche Werte z.B. FFC (First-Fill Complete für vollständig erfüllte Bestellungen), FFP (First-Fill Part Fill für teilweise erfüllte Bestellungen), 
+Bsp: http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
   </si>
   <si>
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -877,7 +1002,7 @@
 </t>
   </si>
   <si>
-    <t>Amount dispensed</t>
+    <t>Abgegebene Menge und Einheit</t>
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
@@ -895,7 +1020,7 @@
     <t>MedicationDispense.daysSupply</t>
   </si>
   <si>
-    <t>Amount of medication expressed as a timing amount</t>
+    <t>Medikamentenmenge, ausgedrückt als zeitliche Menge</t>
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
@@ -917,7 +1042,7 @@
 </t>
   </si>
   <si>
-    <t>When product was packaged and reviewed</t>
+    <t>Verpackungs- und Prüfdatum.</t>
   </si>
   <si>
     <t>The time when the dispensed product was packaged and reviewed.</t>
@@ -935,7 +1060,7 @@
     <t>MedicationDispense.whenHandedOver</t>
   </si>
   <si>
-    <t>When product was given out</t>
+    <t>Der Zeitpunkt, zu dem das abgegebene Produkt dem Patienten oder seinem Vertreter zur Verfügung gestellt wurde.</t>
   </si>
   <si>
     <t>The time the dispensed product was provided to the patient or their representative.</t>
@@ -950,7 +1075,7 @@
     <t>MedicationDispense.destination</t>
   </si>
   <si>
-    <t>Where the medication was sent</t>
+    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identification of the facility/location where the medication was shipped to, as part of the dispense event.</t>
@@ -968,11 +1093,11 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
-    <t>Who collected the medication</t>
+    <t>Person, die das Medikament abgeholt hat. Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identifies the person who picked up the medication.  This will usually be a patient or their caregiver, but some cases exist where it can be a healthcare professional.</t>
@@ -991,7 +1116,7 @@
 </t>
   </si>
   <si>
-    <t>Information about the dispense</t>
+    <t>Zusätzliche Informationen zur Abgabe, die nicht anders dokumentiert werden kann.</t>
   </si>
   <si>
     <t>Extra information about the dispense that could not be conveyed in the other attributes.</t>
@@ -1013,7 +1138,12 @@
 </t>
   </si>
   <si>
-    <t>How the medication is to be used by the patient or administered by the caregiver</t>
+    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
+Wenn sich die Dosis oder Dosierungsrate über den gesamten Verabreichungszeitraum ändern soll 
+(z.B. bei verschreibungspflichtigen Medikamenten mit schrittweiser Dosierungsreduktion), 
+müssen mehrere Dosierungsanweisungen bereitgestellt werden, um die verschiedenen Dosen/Dosierungsraten zu vermitteln. 
+Der Apotheker überprüft die Medikamentenbestellung vor der Abgabe und aktualisiert die Dosierungsanweisung auf der Grundlage 
+des tatsächlich abgegebenen Produkts.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1029,7 +1159,7 @@
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
-    <t>Whether a substitution was performed on the dispense</t>
+    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
@@ -1057,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t>Whether a substitution was or was not performed on the dispense</t>
+    <t>TRUE, wenn der Apotheker ein anderes Medikament oder Produkt als das verschriebene abgegeben hat.</t>
   </si>
   <si>
     <t>True if the dispenser dispensed a different drug or product from what was prescribed.</t>
@@ -1069,7 +1199,7 @@
     <t>MedicationDispense.substitution.type</t>
   </si>
   <si>
-    <t>Code signifying whether a different drug was dispensed from what was prescribed</t>
+    <t>Typ der Substitution: z.B. E equivalent, http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
   </si>
   <si>
     <t>A code signifying whether a different drug was dispensed from what was prescribed.</t>
@@ -1090,7 +1220,7 @@
     <t>MedicationDispense.substitution.reason</t>
   </si>
   <si>
-    <t>Why was substitution made</t>
+    <t>Grund für die Substitution: z.B. OS out of stock, https://hl7.org/fhir/R4/v3/SubstanceAdminSubstitutionReason/vs.html</t>
   </si>
   <si>
     <t>Indicates the reason for the substitution (or lack of substitution) from what was prescribed.</t>
@@ -1111,11 +1241,11 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
-    <t>Who is responsible for the substitution</t>
+    <t>Für die Subistution Verantwortlicher.</t>
   </si>
   <si>
     <t>The person or organization that has primary responsibility for the substitution.</t>
@@ -1138,7 +1268,7 @@
 </t>
   </si>
   <si>
-    <t>Clinical issue with action</t>
+    <t>Referenenz auf DetectedIssue Ressource. Verwendung prüfen.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1157,7 +1287,8 @@
 </t>
   </si>
   <si>
-    <t>A list of relevant lifecycle events</t>
+    <t>Bezeichnet eine Liste von Provenance-Ressourcen, die verschiedene relevante Versionen 
+dieser Ressource dokumentieren. Verwendung prüfen.</t>
   </si>
   <si>
     <t>A summary of the events of interest that have occurred, such as when the dispense was verified.</t>
@@ -1295,6 +1426,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1476,12 +1622,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO46"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1489,7 +1635,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="205.50390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1507,7 +1653,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1646,7 +1792,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1761,7 +1907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1878,7 +2024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1993,7 +2139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2110,7 +2256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2227,7 +2373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2344,7 +2490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2461,7 +2607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2578,7 +2724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2716,7 +2862,7 @@
         <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -2814,7 +2960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2830,7 +2976,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2948,7 +3094,7 @@
         <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>89</v>
@@ -3046,7 +3192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -3119,16 +3265,14 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>171</v>
@@ -3146,10 +3290,10 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3163,12 +3307,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3180,7 +3326,7 @@
         <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3189,17 +3335,15 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3224,13 +3368,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3248,7 +3392,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3263,10 +3407,10 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3278,23 +3422,25 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3303,20 +3449,18 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3341,13 +3485,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3365,10 +3509,10 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>88</v>
@@ -3380,27 +3524,27 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3411,28 +3555,28 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3458,13 +3602,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3482,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3497,27 +3641,27 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3525,30 +3669,32 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3573,34 +3719,32 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>88</v>
@@ -3612,29 +3756,31 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3643,27 +3789,29 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3688,13 +3836,11 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3712,13 +3858,13 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -3727,27 +3873,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3758,7 +3904,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3770,13 +3916,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3827,53 +3973,53 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3885,15 +4031,17 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3930,37 +4078,37 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -3972,20 +4120,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>80</v>
@@ -3997,21 +4145,23 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4059,7 +4209,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4071,13 +4221,13 @@
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4086,38 +4236,38 @@
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>238</v>
@@ -4126,10 +4276,10 @@
         <v>239</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>143</v>
+        <v>241</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4178,25 +4328,25 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>131</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4205,15 +4355,15 @@
         <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4221,33 +4371,33 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4271,31 +4421,31 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4310,27 +4460,27 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4338,10 +4488,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4353,13 +4503,13 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4410,10 +4560,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4425,10 +4575,10 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4440,12 +4590,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4456,7 +4606,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4468,13 +4618,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4525,13 +4675,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4543,10 +4693,10 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -4557,10 +4707,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4568,13 +4718,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -4583,17 +4733,15 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4642,7 +4790,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4657,27 +4805,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4700,13 +4848,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4733,13 +4881,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4757,7 +4905,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4769,41 +4917,41 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>272</v>
+        <v>219</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4815,15 +4963,17 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>276</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4872,74 +5022,78 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>279</v>
+        <v>219</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4987,25 +5141,25 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>285</v>
+        <v>131</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5014,15 +5168,15 @@
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5036,25 +5190,27 @@
         <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>288</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5078,13 +5234,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5102,7 +5258,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5120,24 +5276,24 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5145,13 +5301,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5160,13 +5316,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5217,10 +5373,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5232,27 +5388,27 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5263,7 +5419,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5275,13 +5431,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5332,7 +5488,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5350,24 +5506,24 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5378,10 +5534,10 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5390,15 +5546,17 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5447,7 +5605,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5462,27 +5620,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5493,10 +5651,10 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5505,13 +5663,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>312</v>
+        <v>172</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5538,13 +5696,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>309</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5562,13 +5720,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -5577,27 +5735,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5608,10 +5766,10 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5620,17 +5778,15 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5679,13 +5835,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5697,24 +5853,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5728,7 +5884,7 @@
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5737,13 +5893,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5794,7 +5950,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5812,24 +5968,24 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5843,22 +5999,22 @@
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>228</v>
+        <v>326</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>230</v>
+        <v>328</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5909,7 +6065,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>231</v>
+        <v>325</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5921,44 +6077,44 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -5967,17 +6123,15 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>326</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>135</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6026,78 +6180,74 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>235</v>
+        <v>332</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>293</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>238</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6145,42 +6295,42 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>131</v>
+        <v>340</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>342</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6188,10 +6338,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6203,13 +6353,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6260,13 +6410,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6278,13 +6428,13 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6292,10 +6442,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6306,10 +6456,10 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6318,13 +6468,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>181</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6351,13 +6501,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6375,13 +6525,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6390,27 +6540,27 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>343</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6424,7 +6574,7 @@
         <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6433,15 +6583,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>181</v>
+        <v>357</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6466,13 +6618,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -6490,7 +6642,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6508,13 +6660,13 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>21</v>
@@ -6522,10 +6674,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6536,10 +6688,10 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6548,13 +6700,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>352</v>
+        <v>267</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6605,13 +6757,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6623,35 +6775,35 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6663,17 +6815,15 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>359</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6722,25 +6872,25 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>363</v>
+        <v>219</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6752,16 +6902,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6780,16 +6930,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>365</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>366</v>
+        <v>135</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>222</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6839,7 +6989,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6851,25 +7001,856 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AK48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO53">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI52">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
+    <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
 Sofern eine zugehörige geplante Abgabe vorliegt, können Abweichungen hinsichtlich der Dosierung oder einer möglichen
 Substitution des Medikaments in der durchgeführten Abgabe dokumentiert werden.</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -477,7 +477,7 @@
 </t>
   </si>
   <si>
-    <t>Externer Identifier.</t>
+    <t>Durchgeführte-Abgabe-ID ? Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -505,7 +505,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis. Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Auslösendes Ereignis. Referenz auf Procedure-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -558,7 +558,7 @@
 </t>
   </si>
   <si>
-    <t>Warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
+    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
   </si>
   <si>
     <t>Indicates the reason why a dispense was not performed.</t>
@@ -605,7 +605,7 @@
 </t>
   </si>
   <si>
-    <t>Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Referenz auf DetectedIssue-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
@@ -787,7 +787,7 @@
 </t>
   </si>
   <si>
-    <t>Österreichischer Patient für den die durchgeführte Abgabe ausgestellt wird.</t>
+    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -917,7 +917,9 @@
 </t>
   </si>
   <si>
-    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization; entfernen: Patient, Device, RelatedPerson</t>
+    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization (entfernen: Patient, Device, RelatedPerson), 
+die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
   </si>
   <si>
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
@@ -952,7 +954,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe.</t>
+    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -1138,10 +1140,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
-Wenn sich die Dosis oder Dosierungsrate über den gesamten Verabreichungszeitraum ändern soll 
-(z.B. bei verschreibungspflichtigen Medikamenten mit schrittweiser Dosierungsreduktion), 
-müssen mehrere Dosierungsanweisungen bereitgestellt werden, um die verschiedenen Dosen/Dosierungsraten zu vermitteln. 
+    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. TODO: Dosiervarianten.
 Der Apotheker überprüft die Medikamentenbestellung vor der Abgabe und aktualisiert die Dosierungsanweisung auf der Grundlage 
 des tatsächlich abgegebenen Produkts.</t>
   </si>
@@ -1159,7 +1158,8 @@
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
+    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. 
+Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
@@ -1268,7 +1268,7 @@
 </t>
   </si>
   <si>
-    <t>Referenenz auf DetectedIssue Ressource. Verwendung prüfen.</t>
+    <t>Referenenz auf DetectedIssue Ressource, daher keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. drug-drug interaction, duplicate therapy, dosage alert etc.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,8 +88,8 @@
   </si>
   <si>
     <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
-Sofern eine zugehörige geplante Abgabe vorliegt, können Abweichungen hinsichtlich der Dosierung oder einer möglichen
-Substitution des Medikaments in der durchgeführten Abgabe dokumentiert werden.</t>
+In der durchgeführten Abgabe können Abweichungen hinsichtlich der Dosierung des Medikaments dokumentiert werden.
+Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Einer mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -477,7 +477,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID ? Verwendung prüfen.</t>
+    <t>Durchgeführte-Abgabe-ID. TODO: Verwendung zu prüfen.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -520,7 +520,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status des durchgeführten Abgabe: preparation | in-progress | cancelled | on-hold | completed | entered-in-error | stopped | declined | unknown; http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
+    <t>Status der durchgeführten Abgabe: preparation | in-progress | cancelled | on-hold | completed | entered-in-error | stopped | declined | unknown; http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
 -&gt; VS einschränken</t>
   </si>
   <si>
@@ -938,7 +938,7 @@
 </t>
   </si>
   <si>
-    <t>Ort der Abgabe (Referenz auf Location Ressource). Verwendung prüfen.</t>
+    <t>Ort der Abgabe (Referenz auf Location Ressource). Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>The principal physical location where the dispense was performed.</t>
@@ -1187,7 +1187,7 @@
 </t>
   </si>
   <si>
-    <t>TRUE, wenn der Apotheker ein anderes Medikament oder Produkt als das verschriebene abgegeben hat.</t>
+    <t>Whether a substitution was or was not performed on the dispense</t>
   </si>
   <si>
     <t>True if the dispenser dispensed a different drug or product from what was prescribed.</t>
@@ -1199,7 +1199,7 @@
     <t>MedicationDispense.substitution.type</t>
   </si>
   <si>
-    <t>Typ der Substitution: z.B. E equivalent, http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
+    <t>Code signifying whether a different drug was dispensed from what was prescribed</t>
   </si>
   <si>
     <t>A code signifying whether a different drug was dispensed from what was prescribed.</t>
@@ -1220,7 +1220,7 @@
     <t>MedicationDispense.substitution.reason</t>
   </si>
   <si>
-    <t>Grund für die Substitution: z.B. OS out of stock, https://hl7.org/fhir/R4/v3/SubstanceAdminSubstitutionReason/vs.html</t>
+    <t>Why was substitution made</t>
   </si>
   <si>
     <t>Indicates the reason for the substitution (or lack of substitution) from what was prescribed.</t>
@@ -1241,11 +1241,11 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
-    <t>Für die Subistution Verantwortlicher.</t>
+    <t>Who is responsible for the substitution</t>
   </si>
   <si>
     <t>The person or organization that has primary responsibility for the substitution.</t>
@@ -2843,7 +2843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2859,10 +2859,10 @@
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3539,7 +3539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -4606,7 +4606,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -5171,7 +5171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>279</v>
       </c>
@@ -5187,10 +5187,10 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5865,7 +5865,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>320</v>
       </c>
@@ -5881,10 +5881,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5980,7 +5980,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>325</v>
       </c>
@@ -5996,10 +5996,10 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6672,7 +6672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>362</v>
       </c>
@@ -6688,10 +6688,10 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7253,7 +7253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>375</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7368,7 +7368,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>382</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7483,7 +7483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>389</v>
       </c>
@@ -7499,10 +7499,10 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,8 +520,11 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe: preparation | in-progress | cancelled | on-hold | completed | entered-in-error | stopped | declined | unknown; http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
--&gt; VS einschränken</t>
+    <t>Status der durchgeführten Abgabe: &lt;br&gt;
+"completed": durchgeführte Abgabe ist abgeschlossen &lt;br&gt;
+"entered-in-error": durchgeführte Abgabe wird aufgrund falscher Eingabe storniert &lt;br&gt;
+"stopped": Abgabe wird nicht durchgeführt (Medikament wird abgesetzt) &lt;br&gt;
+http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -611,7 +614,7 @@
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant), https://hl7.org/fhir/R4/valueset-medicationdispense-category.html. Verwendung zu prüfen.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant), https://hl7.org/fhir/R4/valueset-medicationdispense-category.html. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -632,11 +635,12 @@
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
-  </si>
-  <si>
-    <t>Abgegebenes Medikament. Code oder Referenz</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication) &lt;&lt;contained&gt;&gt;
+</t>
+  </si>
+  <si>
+    <t>Abgegebenes Medikament. Das Medikament wird immer in einer contained Medication Ressource dokumentiert, damit 
+Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -645,15 +649,6 @@
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.</t>
   </si>
   <si>
-    <t>A coded concept identifying which substance or product can be dispensed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -669,22 +664,92 @@
     <t>RXD-2-Dispense/Give Code</t>
   </si>
   <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>Angabe mittels Pharmazentralnummer (PZN) aus der ASP-Liste.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].id</t>
+    <t>MedicationDispense.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+</t>
+  </si>
+  <si>
+    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+  </si>
+  <si>
+    <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>PID-3-Patient ID List</t>
+  </si>
+  <si>
+    <t>MedicationDispense.context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der durchgeführten Abgabe.</t>
+  </si>
+  <si>
+    <t>The encounter or episode of care that establishes the context for this event.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN, code="type of encounter or episode"]</t>
+  </si>
+  <si>
+    <t>MedicationDispense.supportingInformation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Referenz auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+  </si>
+  <si>
+    <t>Additional information that supports the medication being dispensed.</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>MedicationDispense.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Durchführende Person</t>
+  </si>
+  <si>
+    <t>Indicates who or what performed the event.</t>
+  </si>
+  <si>
+    <t>Event.performer</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>MedicationDispense.performer.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -703,173 +768,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].extension</t>
+    <t>MedicationDispense.performer.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x]:medicationCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>MedicationDispense.medication[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>MedicationDispense.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
-</t>
-  </si>
-  <si>
-    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
-  </si>
-  <si>
-    <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration-&gt;subject-&gt;Patient.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].role[classCode=PAT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>PID-3-Patient ID List</t>
-  </si>
-  <si>
-    <t>MedicationDispense.context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Referenz auf Encounter oder EpisodeOfCare. Verwendung in der durchgeführten Abgabe prüfen.</t>
-  </si>
-  <si>
-    <t>The encounter or episode of care that establishes the context for this event.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN, code="type of encounter or episode"]</t>
-  </si>
-  <si>
-    <t>MedicationDispense.supportingInformation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Referenz auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. 
-Verwendung in der durchgeführten Abgabe prüfen.</t>
-  </si>
-  <si>
-    <t>Additional information that supports the medication being dispensed.</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=PERT].target[A_SupportingClinicalStatement CMET minimal with many different choices of classCodes(ORG, ENC, PROC, SPLY, SBADM, OBS) and each of the act class codes draws from one or more of the following moodCodes (EVN, DEF, INT PRMS, RQO, PRP, APT, ARQ, GOL)]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Durchführende Person</t>
-  </si>
-  <si>
-    <t>Indicates who or what performed the event.</t>
-  </si>
-  <si>
-    <t>Event.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.performer.extension</t>
   </si>
   <si>
     <t>MedicationDispense.performer.modifierExtension</t>
@@ -917,9 +822,9 @@
 </t>
   </si>
   <si>
-    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization (entfernen: Patient, Device, RelatedPerson), 
+    <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
 die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
-auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
+auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
@@ -954,7 +859,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest).</t>
+    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -978,8 +883,17 @@
     <t>MedicationDispense.type</t>
   </si>
   <si>
-    <t>Mögliche Werte z.B. FFC (First-Fill Complete für vollständig erfüllte Bestellungen), FFP (First-Fill Part Fill für teilweise erfüllte Bestellungen), 
-Bsp: http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
+    <t xml:space="preserve">Mögliche Werte z.B. FFC (First-Fill Complete für vollständig erfüllte Bestellungen), FFP (First-Fill Part Fill für teilweise erfüllte Bestellungen), 
+Bsp: http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType  //ffc, ffp, Refill - Part Fill, refill complete: evtl. selbst definieren
+// für leerabgabe: complete-ausprägung; emergency supply offen (OTC), complete
+Der Prozess des „Besorgers“ (wenn ein Arzneimittel nicht lagernd ist und bestellt werden muss) wird in der e-Medikation abgebildet. 
+Dabei wird das Rezept von der Apotheke eingelöst, und die Abgabe wird als Teilabgabe gekennzeichnet 
+(siehe Markierung FFP „First Fill, Part Fill“ oder RFP „Refill - Part Fill“). Die Verordnung wird nicht in den Status EINGELÖST versetzt und es können solange weitere Abgaben dispensiert werden, bis eine Abgabe mit der Markierung RFC „Refill - Complete“ gespeichert wird. Die Kennzeichnung zeigt, dass das Arzneimittel dem Patienten noch nicht ausgehändigt wurde. Die Kennzeichnung zeigt auch, ob alle Packungen einer Verordnung bzw. teilweise Packungen einer Verordnung bestellt werden. Solange eine Abgabe mit der Kennzeichnung „Besorger“ vorhanden ist, muss die Abgabe mit der eMED-ID abrufbar sein.
+"FFC": First Fill - Complete:  &lt;br&gt;
+"FFP": First Fill - Part Fill &lt;br&gt;  
+"RFP": Refill - Part Fill &lt;br&gt; 
+"RFC": Refill - Complete &lt;br&gt;
+</t>
   </si>
   <si>
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -1004,7 +918,7 @@
 </t>
   </si>
   <si>
-    <t>Abgegebene Menge und Einheit</t>
+    <t>Abgegebene Menge und Einheit.</t>
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
@@ -1622,10 +1536,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.5078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1653,7 +1567,7 @@
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3656,7 +3570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -3719,26 +3633,28 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>196</v>
@@ -3756,37 +3672,35 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
@@ -3801,16 +3715,16 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3836,11 +3750,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3858,10 +3774,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3873,27 +3789,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3904,7 +3820,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3916,13 +3832,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3973,7 +3889,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3985,13 +3901,13 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -4005,21 +3921,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4031,17 +3947,15 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4078,19 +3992,19 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4102,16 +4016,16 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4120,9 +4034,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>227</v>
@@ -4136,16 +4050,16 @@
         <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>228</v>
@@ -4156,12 +4070,8 @@
       <c r="M22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>232</v>
-      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4209,7 +4119,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4224,10 +4134,10 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4236,15 +4146,15 @@
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4264,23 +4174,19 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4328,7 +4234,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4340,13 +4246,13 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4355,47 +4261,47 @@
         <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>135</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4445,74 +4351,78 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>255</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4560,25 +4470,25 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>131</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4592,10 +4502,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4618,16 +4528,18 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4651,13 +4563,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4675,13 +4587,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4693,10 +4605,10 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -4707,10 +4619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4733,13 +4645,13 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4790,13 +4702,13 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -4805,10 +4717,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4822,10 +4734,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4836,7 +4748,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4848,13 +4760,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4905,7 +4817,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4917,13 +4829,13 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4935,26 +4847,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4963,16 +4875,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>266</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5022,7 +4934,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5034,25 +4946,25 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>274</v>
       </c>
@@ -5061,39 +4973,35 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5117,13 +5025,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5141,42 +5049,42 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>131</v>
-      </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5184,13 +5092,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5199,18 +5107,16 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>282</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5234,13 +5140,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5258,7 +5164,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5282,18 +5188,18 @@
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5301,13 +5207,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5316,13 +5222,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5373,10 +5279,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>88</v>
@@ -5388,7 +5294,7 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>291</v>
@@ -5400,15 +5306,15 @@
         <v>21</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5428,16 +5334,16 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5488,7 +5394,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5506,24 +5412,24 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5531,7 +5437,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -5546,17 +5452,15 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5605,13 +5509,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -5620,27 +5524,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AO34" t="s" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>305</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>306</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5648,13 +5552,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5663,13 +5567,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>172</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5696,13 +5600,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5720,7 +5624,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5738,24 +5642,24 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>313</v>
-      </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5763,13 +5667,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5778,13 +5682,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5835,13 +5739,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5853,24 +5757,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5881,10 +5785,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5893,13 +5797,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5950,13 +5854,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -5965,27 +5869,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO37" t="s" s="2">
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
         <v>324</v>
       </c>
-    </row>
-    <row r="38" hidden="true">
-      <c r="A38" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5996,27 +5900,29 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6065,13 +5971,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -6089,18 +5995,18 @@
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6108,13 +6014,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6123,13 +6029,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>326</v>
+        <v>228</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6180,7 +6086,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6195,27 +6101,27 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6226,7 +6132,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6238,13 +6144,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>293</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>235</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
+        <v>236</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6295,7 +6201,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>337</v>
+        <v>237</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6307,41 +6213,41 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>340</v>
+        <v>238</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6353,15 +6259,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>344</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6410,7 +6318,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>241</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6422,34 +6330,34 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>347</v>
+        <v>238</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6459,25 +6367,29 @@
         <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6525,7 +6437,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>246</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6537,13 +6449,13 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>354</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6552,15 +6464,15 @@
         <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>355</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6568,13 +6480,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6583,17 +6495,15 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6642,13 +6552,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -6660,7 +6570,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6674,10 +6584,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6688,7 +6598,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6700,13 +6610,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6733,13 +6643,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6757,7 +6667,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6775,24 +6685,24 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>365</v>
+        <v>278</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6803,7 +6713,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6815,13 +6725,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>216</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>217</v>
+        <v>352</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6848,13 +6758,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>353</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6872,31 +6782,31 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>350</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -6904,14 +6814,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6930,17 +6840,15 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>358</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>135</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6989,7 +6897,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7001,19 +6909,19 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>219</v>
+        <v>361</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -7021,46 +6929,44 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>365</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>277</v>
+        <v>367</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7108,7 +7014,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>278</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7120,13 +7026,13 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>131</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
@@ -7151,10 +7057,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7174,7 +7080,9 @@
       <c r="M48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7226,10 +7134,10 @@
         <v>370</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7241,7 +7149,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7250,590 +7158,11 @@
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO53">
+  <autoFilter ref="A1:AO48">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7843,7 +7172,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI47">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -430,38 +430,65 @@
     <t>MedicationDispense.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationDispense.extension:renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction}
+</t>
+  </si>
+  <si>
+    <t>Vollständige Darstellung der Dosierungsanweisungen</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationDispense.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -769,6 +796,9 @@
   </si>
   <si>
     <t>MedicationDispense.performer.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1536,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO48"/>
+  <dimension ref="A1:AO49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
@@ -2530,7 +2560,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2549,17 +2579,15 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2596,16 +2624,14 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2626,7 +2652,7 @@
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2643,43 +2669,41 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2727,7 +2751,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2736,7 +2760,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2759,44 +2783,46 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2844,7 +2870,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2856,19 +2882,19 @@
         <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>21</v>
@@ -2876,10 +2902,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2902,15 +2928,17 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -2959,7 +2987,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2980,21 +3008,21 @@
         <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3002,32 +3030,30 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3052,13 +3078,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3076,13 +3102,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -3091,27 +3117,27 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AM13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" hidden="true">
-      <c r="A14" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3119,30 +3145,32 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3167,32 +3195,34 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>88</v>
@@ -3204,31 +3234,29 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3240,7 +3268,7 @@
         <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3249,13 +3277,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3282,31 +3310,29 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3321,10 +3347,10 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3336,15 +3362,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
@@ -3354,10 +3380,10 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -3366,13 +3392,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3399,13 +3425,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3423,7 +3449,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3438,10 +3464,10 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3455,12 +3481,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3481,17 +3509,15 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3516,13 +3542,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3540,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3555,10 +3581,10 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3570,12 +3596,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3583,22 +3609,22 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>198</v>
@@ -3633,13 +3659,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3657,10 +3683,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>88</v>
@@ -3672,27 +3698,27 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3715,16 +3741,16 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3774,10 +3800,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3789,27 +3815,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO19" t="s" s="2">
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>214</v>
       </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3817,30 +3843,32 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3889,7 +3917,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3910,21 +3938,21 @@
         <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3947,13 +3975,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4004,13 +4032,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -4019,13 +4047,13 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4034,12 +4062,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4047,13 +4075,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -4062,13 +4090,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4119,7 +4147,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4134,13 +4162,13 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4149,12 +4177,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4162,13 +4190,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4177,13 +4205,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4234,25 +4262,25 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4266,21 +4294,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4292,17 +4320,15 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4351,25 +4377,25 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4383,14 +4409,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4403,26 +4429,24 @@
         <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4470,7 +4494,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4488,7 +4512,7 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4502,43 +4526,45 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4563,13 +4589,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4587,25 +4613,25 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>131</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4617,12 +4643,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4630,13 +4656,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -4645,16 +4671,18 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4678,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4702,10 +4730,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>88</v>
@@ -4717,10 +4745,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4732,12 +4760,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4745,13 +4773,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4760,13 +4788,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4817,10 +4845,10 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -4832,10 +4860,10 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4847,12 +4875,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4863,10 +4891,10 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4875,17 +4903,15 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4934,13 +4960,13 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -4949,19 +4975,19 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -4977,7 +5003,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -4992,15 +5018,17 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5025,13 +5053,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5055,7 +5083,7 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5064,27 +5092,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5107,13 +5135,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5140,13 +5168,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5164,7 +5192,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5182,24 +5210,24 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5207,13 +5235,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5222,13 +5250,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5279,7 +5307,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5297,24 +5325,24 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5334,16 +5362,16 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5394,7 +5422,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5412,24 +5440,24 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5437,28 +5465,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5509,7 +5537,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5524,27 +5552,27 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5552,13 +5580,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5567,13 +5595,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>261</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5624,7 +5652,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5639,27 +5667,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5682,13 +5710,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5739,13 +5767,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5757,24 +5785,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5785,10 +5813,10 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5797,13 +5825,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5854,7 +5882,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5869,27 +5897,27 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5912,17 +5940,15 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -5971,7 +5997,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5986,10 +6012,10 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>330</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5998,15 +6024,15 @@
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6017,10 +6043,10 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6029,15 +6055,17 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6086,13 +6114,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6104,13 +6132,13 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
@@ -6118,10 +6146,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6132,7 +6160,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6144,13 +6172,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>236</v>
+        <v>341</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6201,7 +6229,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6213,19 +6241,19 @@
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6233,21 +6261,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6259,17 +6287,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6318,25 +6344,25 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6350,14 +6376,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6370,26 +6396,24 @@
         <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6437,7 +6461,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6455,7 +6479,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6469,42 +6493,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>339</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>253</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6552,25 +6580,25 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>255</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>342</v>
+        <v>131</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6584,10 +6612,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6595,7 +6623,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6610,13 +6638,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6643,34 +6671,34 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AA44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>88</v>
@@ -6685,24 +6713,24 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>278</v>
+        <v>351</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6713,7 +6741,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6725,13 +6753,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6758,13 +6786,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6782,13 +6810,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -6800,24 +6828,24 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6840,13 +6868,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>358</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6873,13 +6901,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6897,7 +6925,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6915,13 +6943,13 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -6929,21 +6957,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -6955,17 +6983,15 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7014,7 +7040,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7032,13 +7058,13 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7046,14 +7072,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7072,16 +7098,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7131,7 +7157,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7149,7 +7175,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7158,11 +7184,128 @@
         <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO48">
+  <autoFilter ref="A1:AO49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7172,7 +7315,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI47">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -547,14 +547,16 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe: &lt;br&gt;
-"completed": durchgeführte Abgabe ist abgeschlossen &lt;br&gt;
-"entered-in-error": durchgeführte Abgabe wird aufgrund falscher Eingabe storniert &lt;br&gt;
-"stopped": Abgabe wird nicht durchgeführt (Medikament wird abgesetzt) &lt;br&gt;
-http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the set of dispense events.</t>
+    <t>Status der durchgeführten Abgabe: completed | entered-in-error | stopped. Details siehe Definition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* **\"completed\"**: Die durchgeführte Abgabe ist abgeschlossen. 
+* **\"entered-in-error\"**: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.
+* **\"stopped\"**: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt). 
+http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
+TODO: zu prüfen: 
+* ob es einen Status in-progress / preparation geben soll, z.B. wenn Bestellvorgang gestartet wurde und der typ First Fill - Part Fill ist.
+* Technische Prüfungen bezüglich Abhängigkeiten von status, typ, Rezeptart? automatisch geprüft werden? Falls der Status vom Typ der geplanten Abgabe (Rezeptart) abhängig sein kann (z.B. in-progress bei Bestellung o.ä.), evtl Operation </t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -745,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -827,7 +829,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -948,7 +950,7 @@
 </t>
   </si>
   <si>
-    <t>Abgegebene Menge und Einheit.</t>
+    <t>Abgegebene Packungsanzahl.</t>
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
@@ -1021,7 +1023,7 @@
     <t>MedicationDispense.destination</t>
   </si>
   <si>
-    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Verwendung prüfen.</t>
+    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Identification of the facility/location where the medication was shipped to, as part of the dispense event.</t>
@@ -1039,11 +1041,11 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
-    <t>Person, die das Medikament abgeholt hat. Verwendung prüfen.</t>
+    <t>Person, die das Medikament abgeholt hat. Referenz auf Patient oder Practitioner. Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Identifies the person who picked up the medication.  This will usually be a patient or their caregiver, but some cases exist where it can be a healthcare professional.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,7 +891,9 @@
 </t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
+    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.
+zu prüfen (gemäß CDA): 'Ohne Verordnungsbezug kann nur die Abgabe jener OTC-Präparate in der e-Medikation 
+gespeichert werden, die auch wechselwirkungsrelevant sind.'</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,7 +467,11 @@
     <t>Vollständige Darstellung der Dosierungsanweisungen</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -2706,7 +2710,9 @@
       <c r="M10" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -2764,7 +2770,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2773,7 +2779,7 @@
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>21</v>
@@ -2787,14 +2793,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2816,16 +2822,16 @@
         <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -2874,7 +2880,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2906,10 +2912,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2932,16 +2938,16 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2991,7 +2997,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3006,16 +3012,16 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
@@ -3023,10 +3029,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3049,13 +3055,13 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3106,7 +3112,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3121,10 +3127,10 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3138,10 +3144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3167,13 +3173,13 @@
         <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3199,13 +3205,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3223,7 +3229,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>88</v>
@@ -3238,16 +3244,16 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3255,10 +3261,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3281,13 +3287,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3314,29 +3320,29 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3351,10 +3357,10 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3368,13 +3374,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>21</v>
@@ -3396,13 +3402,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3429,13 +3435,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3453,7 +3459,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3468,10 +3474,10 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3485,13 +3491,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
@@ -3513,13 +3519,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3570,7 +3576,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3585,10 +3591,10 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3602,10 +3608,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3628,16 +3634,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3666,10 +3672,10 @@
         <v>112</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3687,7 +3693,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3705,7 +3711,7 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3719,10 +3725,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3745,16 +3751,16 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3804,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>88</v>
@@ -3819,27 +3825,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3862,16 +3868,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3921,7 +3927,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3936,27 +3942,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3979,13 +3985,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4036,7 +4042,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4051,10 +4057,10 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4068,10 +4074,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4094,13 +4100,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4151,7 +4157,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4169,10 +4175,10 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4183,10 +4189,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4209,13 +4215,13 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4266,7 +4272,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4281,10 +4287,10 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4298,10 +4304,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4324,13 +4330,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4381,7 +4387,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4399,7 +4405,7 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4413,14 +4419,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4442,13 +4448,13 @@
         <v>133</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4498,7 +4504,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4516,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4530,14 +4536,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4559,16 +4565,16 @@
         <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4617,7 +4623,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4649,10 +4655,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4675,17 +4681,17 @@
         <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4710,13 +4716,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4734,7 +4740,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4752,7 +4758,7 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4766,10 +4772,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4792,13 +4798,13 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4849,7 +4855,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -4864,10 +4870,10 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>21</v>
@@ -4881,10 +4887,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4907,13 +4913,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4964,7 +4970,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4982,7 +4988,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4996,10 +5002,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5022,16 +5028,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5081,7 +5087,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5096,27 +5102,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5139,13 +5145,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5172,13 +5178,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5196,7 +5202,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5214,24 +5220,24 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5254,13 +5260,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5311,7 +5317,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5329,24 +5335,24 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5369,13 +5375,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5426,7 +5432,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5444,7 +5450,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5453,15 +5459,15 @@
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5484,13 +5490,13 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5541,7 +5547,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5559,24 +5565,24 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5599,13 +5605,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5656,7 +5662,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5671,27 +5677,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5714,13 +5720,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5771,7 +5777,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5789,24 +5795,24 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5829,13 +5835,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5886,7 +5892,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5904,13 +5910,13 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -5918,10 +5924,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5944,13 +5950,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6001,7 +6007,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6016,10 +6022,10 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -6028,15 +6034,15 @@
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6059,16 +6065,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6118,7 +6124,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6136,7 +6142,7 @@
         <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6150,10 +6156,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6176,13 +6182,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6233,7 +6239,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6251,13 +6257,13 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6265,10 +6271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6291,13 +6297,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6348,7 +6354,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6366,7 +6372,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6380,14 +6386,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6409,13 +6415,13 @@
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6465,7 +6471,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6483,7 +6489,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6497,14 +6503,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6526,16 +6532,16 @@
         <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6584,7 +6590,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6616,10 +6622,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6642,13 +6648,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6699,7 +6705,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6717,7 +6723,7 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6731,10 +6737,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6757,13 +6763,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6790,13 +6796,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6814,7 +6820,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6832,24 +6838,24 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6872,13 +6878,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6905,13 +6911,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6929,7 +6935,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6947,13 +6953,13 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>21</v>
@@ -6961,10 +6967,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6987,13 +6993,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7044,7 +7050,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7062,13 +7068,13 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7076,14 +7082,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7102,16 +7108,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7161,7 +7167,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7179,7 +7185,7 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7193,10 +7199,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7219,16 +7225,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7278,7 +7284,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7296,7 +7302,7 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,7 +508,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. TODO: Verwendung zu prüfen.</t>
+    <t>Durchgeführte-Abgabe-ID.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -536,7 +536,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis. Referenz auf Procedure-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -551,16 +551,10 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe: completed | entered-in-error | stopped. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* **\"completed\"**: Die durchgeführte Abgabe ist abgeschlossen. 
-* **\"entered-in-error\"**: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.
-* **\"stopped\"**: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt). 
-http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
-TODO: zu prüfen: 
-* ob es einen Status in-progress / preparation geben soll, z.B. wenn Bestellvorgang gestartet wurde und der typ First Fill - Part Fill ist.
-* Technische Prüfungen bezüglich Abhängigkeiten von status, typ, Rezeptart? automatisch geprüft werden? Falls der Status vom Typ der geplanten Abgabe (Rezeptart) abhängig sein kann (z.B. in-progress bei Bestellung o.ä.), evtl Operation </t>
+    <t>Status der durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the set of dispense events.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -594,7 +588,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
+    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
   </si>
   <si>
     <t>Indicates the reason why a dispense was not performed.</t>
@@ -628,7 +622,7 @@
     <t>statusReasonCodeableConcept</t>
   </si>
   <si>
-    <t>Bsp: https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
+    <t>Grund für den aktuellen Status als Code. (ex) https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]:statusReasonReference</t>
@@ -641,13 +635,13 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf DetectedIssue-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant), https://hl7.org/fhir/R4/valueset-medicationdispense-category.html. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -833,7 +827,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -859,7 +853,7 @@
   </si>
   <si>
     <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
-die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+der/die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
 auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -895,9 +889,7 @@
 </t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.
-zu prüfen (gemäß CDA): 'Ohne Verordnungsbezug kann nur die Abgabe jener OTC-Präparate in der e-Medikation 
-gespeichert werden, die auch wechselwirkungsrelevant sind.'</t>
+    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -921,17 +913,7 @@
     <t>MedicationDispense.type</t>
   </si>
   <si>
-    <t xml:space="preserve">Mögliche Werte z.B. FFC (First-Fill Complete für vollständig erfüllte Bestellungen), FFP (First-Fill Part Fill für teilweise erfüllte Bestellungen), 
-Bsp: http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType  //ffc, ffp, Refill - Part Fill, refill complete: evtl. selbst definieren
-// für leerabgabe: complete-ausprägung; emergency supply offen (OTC), complete
-Der Prozess des „Besorgers“ (wenn ein Arzneimittel nicht lagernd ist und bestellt werden muss) wird in der e-Medikation abgebildet. 
-Dabei wird das Rezept von der Apotheke eingelöst, und die Abgabe wird als Teilabgabe gekennzeichnet 
-(siehe Markierung FFP „First Fill, Part Fill“ oder RFP „Refill - Part Fill“). Die Verordnung wird nicht in den Status EINGELÖST versetzt und es können solange weitere Abgaben dispensiert werden, bis eine Abgabe mit der Markierung RFC „Refill - Complete“ gespeichert wird. Die Kennzeichnung zeigt, dass das Arzneimittel dem Patienten noch nicht ausgehändigt wurde. Die Kennzeichnung zeigt auch, ob alle Packungen einer Verordnung bzw. teilweise Packungen einer Verordnung bestellt werden. Solange eine Abgabe mit der Kennzeichnung „Besorger“ vorhanden ist, muss die Abgabe mit der eMED-ID abrufbar sein.
-"FFC": First Fill - Complete:  &lt;br&gt;
-"FFP": First Fill - Part Fill &lt;br&gt;  
-"RFP": Refill - Part Fill &lt;br&gt; 
-"RFC": Refill - Complete &lt;br&gt;
-</t>
+    <t>Art der Abgabe (z.B. für Teilabgaben). Mögliche Ausprägungen: [FFC | FFP | RFP | RFC | EM]. Bedeutung: FFC: First Fill - Complete | FFP: First Fill - Part Fill | RFP: Refill - Part Fill | RFC: Refill - Complete | EM: Emergency Supply.</t>
   </si>
   <si>
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -974,7 +956,7 @@
     <t>MedicationDispense.daysSupply</t>
   </si>
   <si>
-    <t>Medikamentenmenge, ausgedrückt als zeitliche Menge</t>
+    <t>Tage, für die die abgegebene Menge ausreicht</t>
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
@@ -996,7 +978,7 @@
 </t>
   </si>
   <si>
-    <t>Verpackungs- und Prüfdatum.</t>
+    <t>Zeitpunkt, zu dem das Produkt verpackt und geprüft wurde.</t>
   </si>
   <si>
     <t>The time when the dispensed product was packaged and reviewed.</t>
@@ -1092,9 +1074,8 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. TODO: Dosiervarianten.
-Der Apotheker überprüft die Medikamentenbestellung vor der Abgabe und aktualisiert die Dosierungsanweisung auf der Grundlage 
-des tatsächlich abgegebenen Produkts.</t>
+    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
+Der Apotheker überprüft die Medikamentenverordnung vor der Abgabe und passt die Dosierungsanweisung gegebenenfalls auf Grundlage des tatsächlich abgegebenen Produkts an.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1110,8 +1091,7 @@
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. 
-Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
+    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
@@ -1220,7 +1200,7 @@
 </t>
   </si>
   <si>
-    <t>Referenenz auf DetectedIssue Ressource, daher keine Verwendung in durchgeführter Abgabe.</t>
+    <t>Referenenz auf DetectedIssue Ressource. Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1240,7 +1220,7 @@
   </si>
   <si>
     <t>Bezeichnet eine Liste von Provenance-Ressourcen, die verschiedene relevante Versionen 
-dieser Ressource dokumentieren. Verwendung prüfen.</t>
+dieser Ressource dokumentieren.</t>
   </si>
   <si>
     <t>A summary of the events of interest that have occurred, such as when the dispense was verified.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -267,7 +267,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zum Medikationsplan. Verwendet R5 Backport Extensions.</t>
+    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zur geplanten Abgabe. Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-md-durchgefuehrte-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
